--- a/work1-ledger-cleanup/qa_report.xlsx
+++ b/work1-ledger-cleanup/qa_report.xlsx
@@ -463,7 +463,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>98</v>
+        <v>102</v>
       </c>
     </row>
     <row r="4">
@@ -473,7 +473,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="5">
@@ -483,7 +483,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="6">
@@ -509,14 +509,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E99"/>
+  <dimension ref="A1:E103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="7" customWidth="1" min="3" max="3"/>
     <col width="9" customWidth="1" min="4" max="4"/>
-    <col width="34" customWidth="1" min="5" max="5"/>
+    <col width="50" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2095,20 +2095,20 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>土被りの欠損(SAFIELD003)</t>
+          <t>管種×年代の整合(塩ビ系)</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>要確認</t>
+          <t>NG</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>1660</v>
+        <v>1</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>欠損率 7.8%</t>
+          <t>JSWAS K-1 制定(1974)より前の施工年度。桁誤り・管種誤記・更生の未反映等の疑い</t>
         </is>
       </c>
     </row>
@@ -2120,20 +2120,20 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>土被り異常値(SAFIELD003)</t>
+          <t>土被りの欠損(SAFIELD003)</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>NG</t>
+          <t>要確認</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>141</v>
+        <v>1660</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>許容 0.0-15.0m。負値・桁違いを検出</t>
+          <t>欠損率 7.8%</t>
         </is>
       </c>
     </row>
@@ -2145,20 +2145,20 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>土被りの欠損(SAFIELD004)</t>
+          <t>土被り異常値(SAFIELD003)</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>要確認</t>
+          <t>NG</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>2027</v>
+        <v>141</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>欠損率 9.6%</t>
+          <t>許容 0.0-15.0m。負値・桁違いを検出</t>
         </is>
       </c>
     </row>
@@ -2170,32 +2170,32 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>土被り異常値(SAFIELD004)</t>
+          <t>土被りの欠損(SAFIELD004)</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>NG</t>
+          <t>要確認</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>189</v>
+        <v>2027</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>許容 0.0-15.0m。負値・桁違いを検出</t>
+          <t>欠損率 9.6%</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>下水_マンホール</t>
+          <t>下水_管渠</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>座標系定義(.prj)</t>
+          <t>土被り異常値(SAFIELD004)</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2204,11 +2204,11 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>1</v>
+        <v>189</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>空または欠落。座標範囲からの推定と検証が必要</t>
+          <t>許容 0.0-15.0m。負値・桁違いを検出</t>
         </is>
       </c>
     </row>
@@ -2220,18 +2220,22 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>属性定義XML</t>
+          <t>座標系定義(.prj)</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>NG</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>0</v>
-      </c>
-      <c r="E72" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>空または欠落。座標範囲からの推定と検証が必要</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -2241,16 +2245,16 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>レコード数</t>
+          <t>属性定義XML</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>20689</v>
+        <v>0</v>
       </c>
       <c r="E73" t="inlineStr"/>
     </row>
@@ -2262,16 +2266,16 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>空ジオメトリ</t>
+          <t>レコード数</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>0</v>
+        <v>20689</v>
       </c>
       <c r="E74" t="inlineStr"/>
     </row>
@@ -2283,16 +2287,16 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>SAUID重複</t>
+          <t>空ジオメトリ</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>NG</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E75" t="inlineStr"/>
     </row>
@@ -2304,22 +2308,18 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>表示様式(SASTYLEID)の混在</t>
+          <t>SAUID重複</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>要確認</t>
+          <t>NG</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>31</v>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>複数様式が1ファイルに混在。分析前に分類が必要</t>
-        </is>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="E76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>年度の欠損</t>
+          <t>表示様式(SASTYLEID)の混在</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -2338,11 +2338,11 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>2616</v>
+        <v>31</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>欠損率 12.6%</t>
+          <t>複数様式が1ファイルに混在。分析前に分類が必要</t>
         </is>
       </c>
     </row>
@@ -2354,110 +2354,122 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>年度の範囲外</t>
+          <t>年度の欠損</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>要確認</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>0</v>
+        <v>2616</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>1900年未満または未来(暦年基準)</t>
+          <t>欠損率 12.6%</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>下水_取付管</t>
+          <t>下水_マンホール</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>座標系定義(.prj)</t>
+          <t>年度の範囲外</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>NG</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>空または欠落。座標範囲からの推定と検証が必要</t>
+          <t>1900年未満または未来(暦年基準)</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>下水_取付管</t>
+          <t>下水_マンホール</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>属性定義XML</t>
+          <t>人孔キーの欠損</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>NG</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>0</v>
-      </c>
-      <c r="E80" t="inlineStr"/>
+        <v>1726</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>施設を特定するキーが空</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>下水_取付管</t>
+          <t>下水_マンホール</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>レコード数</t>
+          <t>人孔キーの重複(系統内)</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>NG</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>39443</v>
-      </c>
-      <c r="E81" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>全体重複 2507 のうち系統内の真の重複は 2。残りは系統別採番(キーは系統内でのみ一意)によるもの</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>下水_取付管</t>
+          <t>下水_マンホール</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>空ジオメトリ</t>
+          <t>人孔キーの重複(全体)</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>要確認</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>0</v>
-      </c>
-      <c r="E82" t="inlineStr"/>
+        <v>2507</v>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>系統をまたぐ再利用を含む</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -2467,7 +2479,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>延長ほぼゼロの線</t>
+          <t>座標系定義(.prj)</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -2480,7 +2492,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>0.01(座標単位)未満。CRS未定義時は単位に注意</t>
+          <t>空または欠落。座標範囲からの推定と検証が必要</t>
         </is>
       </c>
     </row>
@@ -2492,16 +2504,16 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>SAUID重複</t>
+          <t>属性定義XML</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>NG</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>96</v>
+        <v>0</v>
       </c>
       <c r="E84" t="inlineStr"/>
     </row>
@@ -2513,22 +2525,18 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>表示様式(SASTYLEID)の混在</t>
+          <t>レコード数</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>要確認</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>2</v>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>複数様式が1ファイルに混在。分析前に分類が必要</t>
-        </is>
-      </c>
+        <v>39443</v>
+      </c>
+      <c r="E85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -2538,7 +2546,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>口径の欠損</t>
+          <t>空ジオメトリ</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -2547,13 +2555,9 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>1392</v>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>欠損率 3.5%</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -2563,20 +2567,20 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>口径の未入力(0)</t>
+          <t>延長ほぼゼロの線</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>NG</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>0 は未入力プレースホルダとみなす</t>
+          <t>0.01(座標単位)未満。CRS未定義時は単位に注意</t>
         </is>
       </c>
     </row>
@@ -2588,22 +2592,18 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>口径の上限超過</t>
+          <t>SAUID重複</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>要確認</t>
+          <t>NG</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>179</v>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>300mm 超。大型構造物の実在可能性あり、現地資料と照合</t>
-        </is>
-      </c>
+        <v>96</v>
+      </c>
+      <c r="E88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -2613,57 +2613,57 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>口径の下限未満(入力疑義)</t>
+          <t>表示様式(SASTYLEID)の混在</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>NG</t>
+          <t>要確認</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>50mm 未満(0 を除く)。桁誤り等の疑い</t>
+          <t>複数様式が1ファイルに混在。分析前に分類が必要</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>下水_桝</t>
+          <t>下水_取付管</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>座標系定義(.prj)</t>
+          <t>口径の欠損</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>NG</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>1</v>
+        <v>1392</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>空または欠落。座標範囲からの推定と検証が必要</t>
+          <t>欠損率 3.5%</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>下水_桝</t>
+          <t>下水_取付管</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>属性定義XML</t>
+          <t>口径の未入力(0)</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -2674,49 +2674,61 @@
       <c r="D91" t="n">
         <v>0</v>
       </c>
-      <c r="E91" t="inlineStr"/>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>0 は未入力プレースホルダとみなす</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>下水_桝</t>
+          <t>下水_取付管</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>レコード数</t>
+          <t>口径の上限超過</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>要確認</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>39391</v>
-      </c>
-      <c r="E92" t="inlineStr"/>
+        <v>179</v>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>300mm 超。大型構造物の実在可能性あり、現地資料と照合</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>下水_桝</t>
+          <t>下水_取付管</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>空ジオメトリ</t>
+          <t>口径の下限未満(入力疑義)</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>NG</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>0</v>
-      </c>
-      <c r="E93" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>50mm 未満(0 を除く)。桁誤り等の疑い</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -2726,7 +2738,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>SAUID重複</t>
+          <t>座標系定義(.prj)</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -2735,9 +2747,13 @@
         </is>
       </c>
       <c r="D94" t="n">
-        <v>66</v>
-      </c>
-      <c r="E94" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>空または欠落。座標範囲からの推定と検証が必要</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -2747,22 +2763,18 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>表示様式(SASTYLEID)の混在</t>
+          <t>属性定義XML</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>要確認</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>12</v>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>複数様式が1ファイルに混在。分析前に分類が必要</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -2772,22 +2784,18 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>口径の欠損</t>
+          <t>レコード数</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>1</v>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>欠損率 0.0%</t>
-        </is>
-      </c>
+        <v>39391</v>
+      </c>
+      <c r="E96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -2797,22 +2805,18 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>口径の未入力(0)</t>
+          <t>空ジオメトリ</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>要確認</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>2252</v>
-      </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>0 は未入力プレースホルダとみなす</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -2822,22 +2826,18 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>口径の上限超過</t>
+          <t>SAUID重複</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>要確認</t>
+          <t>NG</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>178</v>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>300mm 超。大型構造物の実在可能性あり、現地資料と照合</t>
-        </is>
-      </c>
+        <v>66</v>
+      </c>
+      <c r="E98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -2847,18 +2847,118 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
+          <t>表示様式(SASTYLEID)の混在</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>12</v>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>複数様式が1ファイルに混在。分析前に分類が必要</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>下水_桝</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>口径の欠損</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>1</v>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>欠損率 0.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>下水_桝</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>口径の未入力(0)</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>2252</v>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>0 は未入力プレースホルダとみなす</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>下水_桝</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>口径の上限超過</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="D102" t="n">
+        <v>178</v>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>300mm 超。大型構造物の実在可能性あり、現地資料と照合</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>下水_桝</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
           <t>口径の下限未満(入力疑義)</t>
         </is>
       </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>NG</t>
-        </is>
-      </c>
-      <c r="D99" t="n">
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="D103" t="n">
         <v>3</v>
       </c>
-      <c r="E99" t="inlineStr">
+      <c r="E103" t="inlineStr">
         <is>
           <t>50mm 未満(0 を除く)。桁誤り等の疑い</t>
         </is>
@@ -2875,14 +2975,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E22"/>
+  <dimension ref="A1:E25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="6" customWidth="1" min="3" max="3"/>
-    <col width="7" customWidth="1" min="4" max="4"/>
-    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="50" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3162,7 +3262,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>土被り異常値(SAFIELD003)</t>
+          <t>管種×年代の整合(塩ビ系)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -3171,11 +3271,11 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>141</v>
+        <v>1</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>許容 0.0-15.0m。負値・桁違いを検出</t>
+          <t>JSWAS K-1 制定(1974)より前の施工年度。桁誤り・管種誤記・更生の未反映等の疑い</t>
         </is>
       </c>
     </row>
@@ -3187,7 +3287,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>土被り異常値(SAFIELD004)</t>
+          <t>土被り異常値(SAFIELD003)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -3196,7 +3296,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>189</v>
+        <v>141</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -3207,12 +3307,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>下水_マンホール</t>
+          <t>下水_管渠</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>座標系定義(.prj)</t>
+          <t>土被り異常値(SAFIELD004)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -3221,11 +3321,11 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1</v>
+        <v>189</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>空または欠落。座標範囲からの推定と検証が必要</t>
+          <t>許容 0.0-15.0m。負値・桁違いを検出</t>
         </is>
       </c>
     </row>
@@ -3237,7 +3337,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>SAUID重複</t>
+          <t>座標系定義(.prj)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -3246,19 +3346,23 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>2</v>
-      </c>
-      <c r="E15" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>空または欠落。座標範囲からの推定と検証が必要</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>下水_取付管</t>
+          <t>下水_マンホール</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>座標系定義(.prj)</t>
+          <t>SAUID重複</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -3267,23 +3371,19 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>1</v>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>空または欠落。座標範囲からの推定と検証が必要</t>
-        </is>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="E16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>下水_取付管</t>
+          <t>下水_マンホール</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>延長ほぼゼロの線</t>
+          <t>人孔キーの欠損</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -3292,23 +3392,23 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
+        <v>1726</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>0.01(座標単位)未満。CRS未定義時は単位に注意</t>
+          <t>施設を特定するキーが空</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>下水_取付管</t>
+          <t>下水_マンホール</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>SAUID重複</t>
+          <t>人孔キーの重複(系統内)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -3317,9 +3417,13 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>96</v>
-      </c>
-      <c r="E18" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>全体重複 2507 のうち系統内の真の重複は 2。残りは系統別採番(キーは系統内でのみ一意)によるもの</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -3329,7 +3433,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>口径の下限未満(入力疑義)</t>
+          <t>座標系定義(.prj)</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -3338,23 +3442,23 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>50mm 未満(0 を除く)。桁誤り等の疑い</t>
+          <t>空または欠落。座標範囲からの推定と検証が必要</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>下水_桝</t>
+          <t>下水_取付管</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>座標系定義(.prj)</t>
+          <t>延長ほぼゼロの線</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -3367,14 +3471,14 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>空または欠落。座標範囲からの推定と検証が必要</t>
+          <t>0.01(座標単位)未満。CRS未定義時は単位に注意</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>下水_桝</t>
+          <t>下水_取付管</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -3388,14 +3492,14 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>66</v>
+        <v>96</v>
       </c>
       <c r="E21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>下水_桝</t>
+          <t>下水_取付管</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -3412,6 +3516,77 @@
         <v>3</v>
       </c>
       <c r="E22" t="inlineStr">
+        <is>
+          <t>50mm 未満(0 を除く)。桁誤り等の疑い</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>下水_桝</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>座標系定義(.prj)</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>1</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>空または欠落。座標範囲からの推定と検証が必要</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>下水_桝</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>SAUID重複</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>66</v>
+      </c>
+      <c r="E24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>下水_桝</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>口径の下限未満(入力疑義)</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>3</v>
+      </c>
+      <c r="E25" t="inlineStr">
         <is>
           <t>50mm 未満(0 を除く)。桁誤り等の疑い</t>
         </is>

--- a/work1-ledger-cleanup/qa_report.xlsx
+++ b/work1-ledger-cleanup/qa_report.xlsx
@@ -11,7 +11,11 @@
     <sheet name="全検査結果" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="NG一覧" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">'サマリ'!$1:$1</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'全検査結果'!$1:$1</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">'NG一覧'!$1:$1</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -425,13 +429,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:B6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -500,6 +504,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -507,15 +512,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="7" customWidth="1" min="3" max="3"/>
-    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="17" customWidth="1" min="1" max="1"/>
+    <col width="27" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="7" customWidth="1" min="4" max="4"/>
     <col width="50" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -2966,6 +2971,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -2973,15 +2979,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
     <col width="6" customWidth="1" min="3" max="3"/>
-    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="6" customWidth="1" min="4" max="4"/>
     <col width="50" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -3594,5 +3600,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
--- a/work1-ledger-cleanup/qa_report.xlsx
+++ b/work1-ledger-cleanup/qa_report.xlsx
@@ -431,11 +431,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:B7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -493,16 +493,29 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>検査実行日</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
           <t>検査基準日</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>2026年</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <printOptions gridLines="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
@@ -2970,6 +2983,7 @@
       </c>
     </row>
   </sheetData>
+  <printOptions gridLines="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
@@ -3599,6 +3613,7 @@
       </c>
     </row>
   </sheetData>
+  <printOptions gridLines="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>

--- a/work1-ledger-cleanup/qa_report.xlsx
+++ b/work1-ledger-cleanup/qa_report.xlsx
@@ -22,7 +22,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -61,10 +64,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -496,10 +503,8 @@
           <t>検査実行日</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2026-08-23</t>
-        </is>
+      <c r="B6" s="2" t="n">
+        <v>46257</v>
       </c>
     </row>
     <row r="7">
@@ -583,7 +588,7 @@
       <c r="D2" t="n">
         <v>1</v>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E2" s="3" t="inlineStr">
         <is>
           <t>空または欠落。座標範囲からの推定と検証が必要</t>
         </is>
@@ -608,7 +613,7 @@
       <c r="D3" t="n">
         <v>0</v>
       </c>
-      <c r="E3" t="inlineStr"/>
+      <c r="E3" s="3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -629,7 +634,7 @@
       <c r="D4" t="n">
         <v>26045</v>
       </c>
-      <c r="E4" t="inlineStr"/>
+      <c r="E4" s="3" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -650,7 +655,7 @@
       <c r="D5" t="n">
         <v>0</v>
       </c>
-      <c r="E5" t="inlineStr"/>
+      <c r="E5" s="3" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -671,7 +676,7 @@
       <c r="D6" t="n">
         <v>0</v>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E6" s="3" t="inlineStr">
         <is>
           <t>0.01(座標単位)未満。CRS未定義時は単位に注意</t>
         </is>
@@ -696,7 +701,7 @@
       <c r="D7" t="n">
         <v>0</v>
       </c>
-      <c r="E7" t="inlineStr"/>
+      <c r="E7" s="3" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -717,7 +722,7 @@
       <c r="D8" t="n">
         <v>11</v>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E8" s="3" t="inlineStr">
         <is>
           <t>複数様式が1ファイルに混在。分析前に分類が必要</t>
         </is>
@@ -742,7 +747,7 @@
       <c r="D9" t="n">
         <v>26</v>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E9" s="3" t="inlineStr">
         <is>
           <t>欠損率 0.1%</t>
         </is>
@@ -767,7 +772,7 @@
       <c r="D10" t="n">
         <v>0</v>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E10" s="3" t="inlineStr">
         <is>
           <t>0 は未入力プレースホルダとみなす</t>
         </is>
@@ -792,7 +797,7 @@
       <c r="D11" t="n">
         <v>0</v>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E11" s="3" t="inlineStr">
         <is>
           <t>3500mm 超。大型構造物の実在可能性あり、現地資料と照合</t>
         </is>
@@ -817,7 +822,7 @@
       <c r="D12" t="n">
         <v>0</v>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E12" s="3" t="inlineStr">
         <is>
           <t>10mm 未満(0 を除く)。桁誤り等の疑い</t>
         </is>
@@ -842,7 +847,7 @@
       <c r="D13" t="n">
         <v>29</v>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E13" s="3" t="inlineStr">
         <is>
           <t>欠損率 0.1%</t>
         </is>
@@ -867,7 +872,7 @@
       <c r="D14" t="n">
         <v>0</v>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="E14" s="3" t="inlineStr">
         <is>
           <t>許容 0.0-15.0m。負値・桁違いを検出</t>
         </is>
@@ -892,7 +897,7 @@
       <c r="D15" t="n">
         <v>1</v>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="E15" s="3" t="inlineStr">
         <is>
           <t>空または欠落。座標範囲からの推定と検証が必要</t>
         </is>
@@ -917,7 +922,7 @@
       <c r="D16" t="n">
         <v>0</v>
       </c>
-      <c r="E16" t="inlineStr"/>
+      <c r="E16" s="3" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -938,7 +943,7 @@
       <c r="D17" t="n">
         <v>45740</v>
       </c>
-      <c r="E17" t="inlineStr"/>
+      <c r="E17" s="3" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -959,7 +964,7 @@
       <c r="D18" t="n">
         <v>0</v>
       </c>
-      <c r="E18" t="inlineStr"/>
+      <c r="E18" s="3" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -980,7 +985,7 @@
       <c r="D19" t="n">
         <v>0</v>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="E19" s="3" t="inlineStr">
         <is>
           <t>0.01(座標単位)未満。CRS未定義時は単位に注意</t>
         </is>
@@ -1005,7 +1010,7 @@
       <c r="D20" t="n">
         <v>30</v>
       </c>
-      <c r="E20" t="inlineStr"/>
+      <c r="E20" s="3" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1026,7 +1031,7 @@
       <c r="D21" t="n">
         <v>1</v>
       </c>
-      <c r="E21" t="inlineStr"/>
+      <c r="E21" s="3" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1047,7 +1052,7 @@
       <c r="D22" t="n">
         <v>1909</v>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="E22" s="3" t="inlineStr">
         <is>
           <t>欠損率 4.2%</t>
         </is>
@@ -1072,7 +1077,7 @@
       <c r="D23" t="n">
         <v>0</v>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="E23" s="3" t="inlineStr">
         <is>
           <t>0 は未入力プレースホルダとみなす</t>
         </is>
@@ -1097,7 +1102,7 @@
       <c r="D24" t="n">
         <v>0</v>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="E24" s="3" t="inlineStr">
         <is>
           <t>3500mm 超。大型構造物の実在可能性あり、現地資料と照合</t>
         </is>
@@ -1122,7 +1127,7 @@
       <c r="D25" t="n">
         <v>0</v>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="E25" s="3" t="inlineStr">
         <is>
           <t>10mm 未満(0 を除く)。桁誤り等の疑い</t>
         </is>
@@ -1147,7 +1152,7 @@
       <c r="D26" t="n">
         <v>1</v>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="E26" s="3" t="inlineStr">
         <is>
           <t>空または欠落。座標範囲からの推定と検証が必要</t>
         </is>
@@ -1172,7 +1177,7 @@
       <c r="D27" t="n">
         <v>0</v>
       </c>
-      <c r="E27" t="inlineStr"/>
+      <c r="E27" s="3" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1193,7 +1198,7 @@
       <c r="D28" t="n">
         <v>10211</v>
       </c>
-      <c r="E28" t="inlineStr"/>
+      <c r="E28" s="3" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1214,7 +1219,7 @@
       <c r="D29" t="n">
         <v>0</v>
       </c>
-      <c r="E29" t="inlineStr"/>
+      <c r="E29" s="3" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1235,7 +1240,7 @@
       <c r="D30" t="n">
         <v>0</v>
       </c>
-      <c r="E30" t="inlineStr"/>
+      <c r="E30" s="3" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1256,7 +1261,7 @@
       <c r="D31" t="n">
         <v>8</v>
       </c>
-      <c r="E31" t="inlineStr">
+      <c r="E31" s="3" t="inlineStr">
         <is>
           <t>複数様式が1ファイルに混在。分析前に分類が必要</t>
         </is>
@@ -1281,7 +1286,7 @@
       <c r="D32" t="n">
         <v>8865</v>
       </c>
-      <c r="E32" t="inlineStr">
+      <c r="E32" s="3" t="inlineStr">
         <is>
           <t>欠損率 86.8%</t>
         </is>
@@ -1306,7 +1311,7 @@
       <c r="D33" t="n">
         <v>1</v>
       </c>
-      <c r="E33" t="inlineStr">
+      <c r="E33" s="3" t="inlineStr">
         <is>
           <t>1900年未満または未来(暦年基準)</t>
         </is>
@@ -1331,7 +1336,7 @@
       <c r="D34" t="n">
         <v>7</v>
       </c>
-      <c r="E34" t="inlineStr">
+      <c r="E34" s="3" t="inlineStr">
         <is>
           <t>欠損率 0.1%</t>
         </is>
@@ -1356,7 +1361,7 @@
       <c r="D35" t="n">
         <v>0</v>
       </c>
-      <c r="E35" t="inlineStr">
+      <c r="E35" s="3" t="inlineStr">
         <is>
           <t>0 は未入力プレースホルダとみなす</t>
         </is>
@@ -1381,7 +1386,7 @@
       <c r="D36" t="n">
         <v>0</v>
       </c>
-      <c r="E36" t="inlineStr">
+      <c r="E36" s="3" t="inlineStr">
         <is>
           <t>3500mm 超。大型構造物の実在可能性あり、現地資料と照合</t>
         </is>
@@ -1406,7 +1411,7 @@
       <c r="D37" t="n">
         <v>0</v>
       </c>
-      <c r="E37" t="inlineStr">
+      <c r="E37" s="3" t="inlineStr">
         <is>
           <t>10mm 未満(0 を除く)。桁誤り等の疑い</t>
         </is>
@@ -1431,7 +1436,7 @@
       <c r="D38" t="n">
         <v>10</v>
       </c>
-      <c r="E38" t="inlineStr">
+      <c r="E38" s="3" t="inlineStr">
         <is>
           <t>欠損率 0.1%</t>
         </is>
@@ -1456,7 +1461,7 @@
       <c r="D39" t="n">
         <v>0</v>
       </c>
-      <c r="E39" t="inlineStr">
+      <c r="E39" s="3" t="inlineStr">
         <is>
           <t>許容 0.0-15.0m。負値・桁違いを検出</t>
         </is>
@@ -1481,7 +1486,7 @@
       <c r="D40" t="n">
         <v>1</v>
       </c>
-      <c r="E40" t="inlineStr">
+      <c r="E40" s="3" t="inlineStr">
         <is>
           <t>空または欠落。座標範囲からの推定と検証が必要</t>
         </is>
@@ -1506,7 +1511,7 @@
       <c r="D41" t="n">
         <v>0</v>
       </c>
-      <c r="E41" t="inlineStr"/>
+      <c r="E41" s="3" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1527,7 +1532,7 @@
       <c r="D42" t="n">
         <v>1343</v>
       </c>
-      <c r="E42" t="inlineStr"/>
+      <c r="E42" s="3" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1548,7 +1553,7 @@
       <c r="D43" t="n">
         <v>0</v>
       </c>
-      <c r="E43" t="inlineStr"/>
+      <c r="E43" s="3" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1569,7 +1574,7 @@
       <c r="D44" t="n">
         <v>0</v>
       </c>
-      <c r="E44" t="inlineStr"/>
+      <c r="E44" s="3" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1590,7 +1595,7 @@
       <c r="D45" t="n">
         <v>2</v>
       </c>
-      <c r="E45" t="inlineStr">
+      <c r="E45" s="3" t="inlineStr">
         <is>
           <t>複数様式が1ファイルに混在。分析前に分類が必要</t>
         </is>
@@ -1615,7 +1620,7 @@
       <c r="D46" t="n">
         <v>1200</v>
       </c>
-      <c r="E46" t="inlineStr">
+      <c r="E46" s="3" t="inlineStr">
         <is>
           <t>欠損率 89.4%</t>
         </is>
@@ -1640,7 +1645,7 @@
       <c r="D47" t="n">
         <v>1</v>
       </c>
-      <c r="E47" t="inlineStr">
+      <c r="E47" s="3" t="inlineStr">
         <is>
           <t>1900年未満または未来(暦年基準)</t>
         </is>
@@ -1665,7 +1670,7 @@
       <c r="D48" t="n">
         <v>0</v>
       </c>
-      <c r="E48" t="inlineStr">
+      <c r="E48" s="3" t="inlineStr">
         <is>
           <t>欠損率 0.0%</t>
         </is>
@@ -1690,7 +1695,7 @@
       <c r="D49" t="n">
         <v>0</v>
       </c>
-      <c r="E49" t="inlineStr">
+      <c r="E49" s="3" t="inlineStr">
         <is>
           <t>0 は未入力プレースホルダとみなす</t>
         </is>
@@ -1715,7 +1720,7 @@
       <c r="D50" t="n">
         <v>0</v>
       </c>
-      <c r="E50" t="inlineStr">
+      <c r="E50" s="3" t="inlineStr">
         <is>
           <t>3500mm 超。大型構造物の実在可能性あり、現地資料と照合</t>
         </is>
@@ -1740,7 +1745,7 @@
       <c r="D51" t="n">
         <v>0</v>
       </c>
-      <c r="E51" t="inlineStr">
+      <c r="E51" s="3" t="inlineStr">
         <is>
           <t>10mm 未満(0 を除く)。桁誤り等の疑い</t>
         </is>
@@ -1765,7 +1770,7 @@
       <c r="D52" t="n">
         <v>0</v>
       </c>
-      <c r="E52" t="inlineStr">
+      <c r="E52" s="3" t="inlineStr">
         <is>
           <t>欠損率 0.0%</t>
         </is>
@@ -1790,7 +1795,7 @@
       <c r="D53" t="n">
         <v>0</v>
       </c>
-      <c r="E53" t="inlineStr">
+      <c r="E53" s="3" t="inlineStr">
         <is>
           <t>許容 0.0-15.0m。負値・桁違いを検出</t>
         </is>
@@ -1815,7 +1820,7 @@
       <c r="D54" t="n">
         <v>1</v>
       </c>
-      <c r="E54" t="inlineStr">
+      <c r="E54" s="3" t="inlineStr">
         <is>
           <t>空または欠落。座標範囲からの推定と検証が必要</t>
         </is>
@@ -1840,7 +1845,7 @@
       <c r="D55" t="n">
         <v>0</v>
       </c>
-      <c r="E55" t="inlineStr"/>
+      <c r="E55" s="3" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -1861,7 +1866,7 @@
       <c r="D56" t="n">
         <v>21223</v>
       </c>
-      <c r="E56" t="inlineStr"/>
+      <c r="E56" s="3" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -1882,7 +1887,7 @@
       <c r="D57" t="n">
         <v>0</v>
       </c>
-      <c r="E57" t="inlineStr"/>
+      <c r="E57" s="3" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -1903,7 +1908,7 @@
       <c r="D58" t="n">
         <v>0</v>
       </c>
-      <c r="E58" t="inlineStr">
+      <c r="E58" s="3" t="inlineStr">
         <is>
           <t>0.01(座標単位)未満。CRS未定義時は単位に注意</t>
         </is>
@@ -1928,7 +1933,7 @@
       <c r="D59" t="n">
         <v>16</v>
       </c>
-      <c r="E59" t="inlineStr"/>
+      <c r="E59" s="3" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -1949,7 +1954,7 @@
       <c r="D60" t="n">
         <v>6</v>
       </c>
-      <c r="E60" t="inlineStr">
+      <c r="E60" s="3" t="inlineStr">
         <is>
           <t>複数様式が1ファイルに混在。分析前に分類が必要</t>
         </is>
@@ -1974,7 +1979,7 @@
       <c r="D61" t="n">
         <v>2436</v>
       </c>
-      <c r="E61" t="inlineStr">
+      <c r="E61" s="3" t="inlineStr">
         <is>
           <t>欠損率 11.5%</t>
         </is>
@@ -1999,7 +2004,7 @@
       <c r="D62" t="n">
         <v>0</v>
       </c>
-      <c r="E62" t="inlineStr">
+      <c r="E62" s="3" t="inlineStr">
         <is>
           <t>1900年未満または未来(暦年基準)</t>
         </is>
@@ -2024,7 +2029,7 @@
       <c r="D63" t="n">
         <v>201</v>
       </c>
-      <c r="E63" t="inlineStr">
+      <c r="E63" s="3" t="inlineStr">
         <is>
           <t>欠損率 0.9%</t>
         </is>
@@ -2049,7 +2054,7 @@
       <c r="D64" t="n">
         <v>0</v>
       </c>
-      <c r="E64" t="inlineStr">
+      <c r="E64" s="3" t="inlineStr">
         <is>
           <t>0 は未入力プレースホルダとみなす</t>
         </is>
@@ -2074,7 +2079,7 @@
       <c r="D65" t="n">
         <v>0</v>
       </c>
-      <c r="E65" t="inlineStr">
+      <c r="E65" s="3" t="inlineStr">
         <is>
           <t>9000mm 超。大型構造物の実在可能性あり、現地資料と照合</t>
         </is>
@@ -2099,7 +2104,7 @@
       <c r="D66" t="n">
         <v>8</v>
       </c>
-      <c r="E66" t="inlineStr">
+      <c r="E66" s="3" t="inlineStr">
         <is>
           <t>100mm 未満(0 を除く)。桁誤り等の疑い</t>
         </is>
@@ -2124,7 +2129,7 @@
       <c r="D67" t="n">
         <v>1</v>
       </c>
-      <c r="E67" t="inlineStr">
+      <c r="E67" s="3" t="inlineStr">
         <is>
           <t>JSWAS K-1 制定(1974)より前の施工年度。桁誤り・管種誤記・更生の未反映等の疑い</t>
         </is>
@@ -2149,7 +2154,7 @@
       <c r="D68" t="n">
         <v>1660</v>
       </c>
-      <c r="E68" t="inlineStr">
+      <c r="E68" s="3" t="inlineStr">
         <is>
           <t>欠損率 7.8%</t>
         </is>
@@ -2174,7 +2179,7 @@
       <c r="D69" t="n">
         <v>141</v>
       </c>
-      <c r="E69" t="inlineStr">
+      <c r="E69" s="3" t="inlineStr">
         <is>
           <t>許容 0.0-15.0m。負値・桁違いを検出</t>
         </is>
@@ -2199,7 +2204,7 @@
       <c r="D70" t="n">
         <v>2027</v>
       </c>
-      <c r="E70" t="inlineStr">
+      <c r="E70" s="3" t="inlineStr">
         <is>
           <t>欠損率 9.6%</t>
         </is>
@@ -2224,7 +2229,7 @@
       <c r="D71" t="n">
         <v>189</v>
       </c>
-      <c r="E71" t="inlineStr">
+      <c r="E71" s="3" t="inlineStr">
         <is>
           <t>許容 0.0-15.0m。負値・桁違いを検出</t>
         </is>
@@ -2249,7 +2254,7 @@
       <c r="D72" t="n">
         <v>1</v>
       </c>
-      <c r="E72" t="inlineStr">
+      <c r="E72" s="3" t="inlineStr">
         <is>
           <t>空または欠落。座標範囲からの推定と検証が必要</t>
         </is>
@@ -2274,7 +2279,7 @@
       <c r="D73" t="n">
         <v>0</v>
       </c>
-      <c r="E73" t="inlineStr"/>
+      <c r="E73" s="3" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -2295,7 +2300,7 @@
       <c r="D74" t="n">
         <v>20689</v>
       </c>
-      <c r="E74" t="inlineStr"/>
+      <c r="E74" s="3" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -2316,7 +2321,7 @@
       <c r="D75" t="n">
         <v>0</v>
       </c>
-      <c r="E75" t="inlineStr"/>
+      <c r="E75" s="3" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -2337,7 +2342,7 @@
       <c r="D76" t="n">
         <v>2</v>
       </c>
-      <c r="E76" t="inlineStr"/>
+      <c r="E76" s="3" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -2358,7 +2363,7 @@
       <c r="D77" t="n">
         <v>31</v>
       </c>
-      <c r="E77" t="inlineStr">
+      <c r="E77" s="3" t="inlineStr">
         <is>
           <t>複数様式が1ファイルに混在。分析前に分類が必要</t>
         </is>
@@ -2383,7 +2388,7 @@
       <c r="D78" t="n">
         <v>2616</v>
       </c>
-      <c r="E78" t="inlineStr">
+      <c r="E78" s="3" t="inlineStr">
         <is>
           <t>欠損率 12.6%</t>
         </is>
@@ -2408,7 +2413,7 @@
       <c r="D79" t="n">
         <v>0</v>
       </c>
-      <c r="E79" t="inlineStr">
+      <c r="E79" s="3" t="inlineStr">
         <is>
           <t>1900年未満または未来(暦年基準)</t>
         </is>
@@ -2433,7 +2438,7 @@
       <c r="D80" t="n">
         <v>1726</v>
       </c>
-      <c r="E80" t="inlineStr">
+      <c r="E80" s="3" t="inlineStr">
         <is>
           <t>施設を特定するキーが空</t>
         </is>
@@ -2458,7 +2463,7 @@
       <c r="D81" t="n">
         <v>2</v>
       </c>
-      <c r="E81" t="inlineStr">
+      <c r="E81" s="3" t="inlineStr">
         <is>
           <t>全体重複 2507 のうち系統内の真の重複は 2。残りは系統別採番(キーは系統内でのみ一意)によるもの</t>
         </is>
@@ -2483,7 +2488,7 @@
       <c r="D82" t="n">
         <v>2507</v>
       </c>
-      <c r="E82" t="inlineStr">
+      <c r="E82" s="3" t="inlineStr">
         <is>
           <t>系統をまたぐ再利用を含む</t>
         </is>
@@ -2508,7 +2513,7 @@
       <c r="D83" t="n">
         <v>1</v>
       </c>
-      <c r="E83" t="inlineStr">
+      <c r="E83" s="3" t="inlineStr">
         <is>
           <t>空または欠落。座標範囲からの推定と検証が必要</t>
         </is>
@@ -2533,7 +2538,7 @@
       <c r="D84" t="n">
         <v>0</v>
       </c>
-      <c r="E84" t="inlineStr"/>
+      <c r="E84" s="3" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -2554,7 +2559,7 @@
       <c r="D85" t="n">
         <v>39443</v>
       </c>
-      <c r="E85" t="inlineStr"/>
+      <c r="E85" s="3" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -2575,7 +2580,7 @@
       <c r="D86" t="n">
         <v>0</v>
       </c>
-      <c r="E86" t="inlineStr"/>
+      <c r="E86" s="3" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -2596,7 +2601,7 @@
       <c r="D87" t="n">
         <v>1</v>
       </c>
-      <c r="E87" t="inlineStr">
+      <c r="E87" s="3" t="inlineStr">
         <is>
           <t>0.01(座標単位)未満。CRS未定義時は単位に注意</t>
         </is>
@@ -2621,7 +2626,7 @@
       <c r="D88" t="n">
         <v>96</v>
       </c>
-      <c r="E88" t="inlineStr"/>
+      <c r="E88" s="3" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -2642,7 +2647,7 @@
       <c r="D89" t="n">
         <v>2</v>
       </c>
-      <c r="E89" t="inlineStr">
+      <c r="E89" s="3" t="inlineStr">
         <is>
           <t>複数様式が1ファイルに混在。分析前に分類が必要</t>
         </is>
@@ -2667,7 +2672,7 @@
       <c r="D90" t="n">
         <v>1392</v>
       </c>
-      <c r="E90" t="inlineStr">
+      <c r="E90" s="3" t="inlineStr">
         <is>
           <t>欠損率 3.5%</t>
         </is>
@@ -2692,7 +2697,7 @@
       <c r="D91" t="n">
         <v>0</v>
       </c>
-      <c r="E91" t="inlineStr">
+      <c r="E91" s="3" t="inlineStr">
         <is>
           <t>0 は未入力プレースホルダとみなす</t>
         </is>
@@ -2717,7 +2722,7 @@
       <c r="D92" t="n">
         <v>179</v>
       </c>
-      <c r="E92" t="inlineStr">
+      <c r="E92" s="3" t="inlineStr">
         <is>
           <t>300mm 超。大型構造物の実在可能性あり、現地資料と照合</t>
         </is>
@@ -2742,7 +2747,7 @@
       <c r="D93" t="n">
         <v>3</v>
       </c>
-      <c r="E93" t="inlineStr">
+      <c r="E93" s="3" t="inlineStr">
         <is>
           <t>50mm 未満(0 を除く)。桁誤り等の疑い</t>
         </is>
@@ -2767,7 +2772,7 @@
       <c r="D94" t="n">
         <v>1</v>
       </c>
-      <c r="E94" t="inlineStr">
+      <c r="E94" s="3" t="inlineStr">
         <is>
           <t>空または欠落。座標範囲からの推定と検証が必要</t>
         </is>
@@ -2792,7 +2797,7 @@
       <c r="D95" t="n">
         <v>0</v>
       </c>
-      <c r="E95" t="inlineStr"/>
+      <c r="E95" s="3" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -2813,7 +2818,7 @@
       <c r="D96" t="n">
         <v>39391</v>
       </c>
-      <c r="E96" t="inlineStr"/>
+      <c r="E96" s="3" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -2834,7 +2839,7 @@
       <c r="D97" t="n">
         <v>0</v>
       </c>
-      <c r="E97" t="inlineStr"/>
+      <c r="E97" s="3" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -2855,7 +2860,7 @@
       <c r="D98" t="n">
         <v>66</v>
       </c>
-      <c r="E98" t="inlineStr"/>
+      <c r="E98" s="3" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -2876,7 +2881,7 @@
       <c r="D99" t="n">
         <v>12</v>
       </c>
-      <c r="E99" t="inlineStr">
+      <c r="E99" s="3" t="inlineStr">
         <is>
           <t>複数様式が1ファイルに混在。分析前に分類が必要</t>
         </is>
@@ -2901,7 +2906,7 @@
       <c r="D100" t="n">
         <v>1</v>
       </c>
-      <c r="E100" t="inlineStr">
+      <c r="E100" s="3" t="inlineStr">
         <is>
           <t>欠損率 0.0%</t>
         </is>
@@ -2926,7 +2931,7 @@
       <c r="D101" t="n">
         <v>2252</v>
       </c>
-      <c r="E101" t="inlineStr">
+      <c r="E101" s="3" t="inlineStr">
         <is>
           <t>0 は未入力プレースホルダとみなす</t>
         </is>
@@ -2951,7 +2956,7 @@
       <c r="D102" t="n">
         <v>178</v>
       </c>
-      <c r="E102" t="inlineStr">
+      <c r="E102" s="3" t="inlineStr">
         <is>
           <t>300mm 超。大型構造物の実在可能性あり、現地資料と照合</t>
         </is>
@@ -2976,7 +2981,7 @@
       <c r="D103" t="n">
         <v>3</v>
       </c>
-      <c r="E103" t="inlineStr">
+      <c r="E103" s="3" t="inlineStr">
         <is>
           <t>50mm 未満(0 を除く)。桁誤り等の疑い</t>
         </is>
@@ -3051,7 +3056,7 @@
       <c r="D2" t="n">
         <v>1</v>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E2" s="3" t="inlineStr">
         <is>
           <t>空または欠落。座標範囲からの推定と検証が必要</t>
         </is>
@@ -3076,7 +3081,7 @@
       <c r="D3" t="n">
         <v>1</v>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E3" s="3" t="inlineStr">
         <is>
           <t>空または欠落。座標範囲からの推定と検証が必要</t>
         </is>
@@ -3101,7 +3106,7 @@
       <c r="D4" t="n">
         <v>30</v>
       </c>
-      <c r="E4" t="inlineStr"/>
+      <c r="E4" s="3" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -3122,7 +3127,7 @@
       <c r="D5" t="n">
         <v>1</v>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E5" s="3" t="inlineStr">
         <is>
           <t>空または欠落。座標範囲からの推定と検証が必要</t>
         </is>
@@ -3147,7 +3152,7 @@
       <c r="D6" t="n">
         <v>1</v>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E6" s="3" t="inlineStr">
         <is>
           <t>1900年未満または未来(暦年基準)</t>
         </is>
@@ -3172,7 +3177,7 @@
       <c r="D7" t="n">
         <v>1</v>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E7" s="3" t="inlineStr">
         <is>
           <t>空または欠落。座標範囲からの推定と検証が必要</t>
         </is>
@@ -3197,7 +3202,7 @@
       <c r="D8" t="n">
         <v>1</v>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E8" s="3" t="inlineStr">
         <is>
           <t>1900年未満または未来(暦年基準)</t>
         </is>
@@ -3222,7 +3227,7 @@
       <c r="D9" t="n">
         <v>1</v>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E9" s="3" t="inlineStr">
         <is>
           <t>空または欠落。座標範囲からの推定と検証が必要</t>
         </is>
@@ -3247,7 +3252,7 @@
       <c r="D10" t="n">
         <v>16</v>
       </c>
-      <c r="E10" t="inlineStr"/>
+      <c r="E10" s="3" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -3268,7 +3273,7 @@
       <c r="D11" t="n">
         <v>8</v>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E11" s="3" t="inlineStr">
         <is>
           <t>100mm 未満(0 を除く)。桁誤り等の疑い</t>
         </is>
@@ -3293,7 +3298,7 @@
       <c r="D12" t="n">
         <v>1</v>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E12" s="3" t="inlineStr">
         <is>
           <t>JSWAS K-1 制定(1974)より前の施工年度。桁誤り・管種誤記・更生の未反映等の疑い</t>
         </is>
@@ -3318,7 +3323,7 @@
       <c r="D13" t="n">
         <v>141</v>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E13" s="3" t="inlineStr">
         <is>
           <t>許容 0.0-15.0m。負値・桁違いを検出</t>
         </is>
@@ -3343,7 +3348,7 @@
       <c r="D14" t="n">
         <v>189</v>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="E14" s="3" t="inlineStr">
         <is>
           <t>許容 0.0-15.0m。負値・桁違いを検出</t>
         </is>
@@ -3368,7 +3373,7 @@
       <c r="D15" t="n">
         <v>1</v>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="E15" s="3" t="inlineStr">
         <is>
           <t>空または欠落。座標範囲からの推定と検証が必要</t>
         </is>
@@ -3393,7 +3398,7 @@
       <c r="D16" t="n">
         <v>2</v>
       </c>
-      <c r="E16" t="inlineStr"/>
+      <c r="E16" s="3" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -3414,7 +3419,7 @@
       <c r="D17" t="n">
         <v>1726</v>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="E17" s="3" t="inlineStr">
         <is>
           <t>施設を特定するキーが空</t>
         </is>
@@ -3439,7 +3444,7 @@
       <c r="D18" t="n">
         <v>2</v>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="E18" s="3" t="inlineStr">
         <is>
           <t>全体重複 2507 のうち系統内の真の重複は 2。残りは系統別採番(キーは系統内でのみ一意)によるもの</t>
         </is>
@@ -3464,7 +3469,7 @@
       <c r="D19" t="n">
         <v>1</v>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="E19" s="3" t="inlineStr">
         <is>
           <t>空または欠落。座標範囲からの推定と検証が必要</t>
         </is>
@@ -3489,7 +3494,7 @@
       <c r="D20" t="n">
         <v>1</v>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="E20" s="3" t="inlineStr">
         <is>
           <t>0.01(座標単位)未満。CRS未定義時は単位に注意</t>
         </is>
@@ -3514,7 +3519,7 @@
       <c r="D21" t="n">
         <v>96</v>
       </c>
-      <c r="E21" t="inlineStr"/>
+      <c r="E21" s="3" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -3535,7 +3540,7 @@
       <c r="D22" t="n">
         <v>3</v>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="E22" s="3" t="inlineStr">
         <is>
           <t>50mm 未満(0 を除く)。桁誤り等の疑い</t>
         </is>
@@ -3560,7 +3565,7 @@
       <c r="D23" t="n">
         <v>1</v>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="E23" s="3" t="inlineStr">
         <is>
           <t>空または欠落。座標範囲からの推定と検証が必要</t>
         </is>
@@ -3585,7 +3590,7 @@
       <c r="D24" t="n">
         <v>66</v>
       </c>
-      <c r="E24" t="inlineStr"/>
+      <c r="E24" s="3" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -3606,7 +3611,7 @@
       <c r="D25" t="n">
         <v>3</v>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="E25" s="3" t="inlineStr">
         <is>
           <t>50mm 未満(0 を除く)。桁誤り等の疑い</t>
         </is>
